--- a/examples/template.xlsx
+++ b/examples/template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti\Dropbox\Retirement\MyProject\Owl\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443E4092-BAB2-44E1-84D9-3B61D144B774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910CC21A-4361-45DE-9D3D-F9467D84AC13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10690" yWindow="7090" windowWidth="19420" windowHeight="11500" xr2:uid="{10BCA99F-290D-43B0-90F7-A2A56377E151}"/>
+    <workbookView xWindow="-21240" yWindow="15780" windowWidth="15045" windowHeight="11700" activeTab="1" xr2:uid="{10BCA99F-290D-43B0-90F7-A2A56377E151}"/>
   </bookViews>
   <sheets>
     <sheet name="Kim" sheetId="1" r:id="rId1"/>
@@ -437,7 +437,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB57614-FCF1-4139-AA0D-31AF55A08D66}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="2" customWidth="1"/>
@@ -476,7 +476,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -489,7 +489,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>2026</v>
+        <v>2021</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -502,7 +502,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>2027</v>
+        <v>2022</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -515,7 +515,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>2028</v>
+        <v>2023</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -528,7 +528,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>2029</v>
+        <v>2024</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -541,7 +541,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>2030</v>
+        <v>2025</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -554,7 +554,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>2031</v>
+        <v>2026</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -567,7 +567,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>2032</v>
+        <v>2027</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -580,7 +580,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>2033</v>
+        <v>2028</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -593,7 +593,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>2034</v>
+        <v>2029</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -606,7 +606,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>2035</v>
+        <v>2030</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -619,7 +619,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>2036</v>
+        <v>2031</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -632,7 +632,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>2037</v>
+        <v>2032</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -645,7 +645,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>2038</v>
+        <v>2033</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -658,7 +658,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>2039</v>
+        <v>2034</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -671,7 +671,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>2040</v>
+        <v>2035</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -684,7 +684,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>2041</v>
+        <v>2036</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -697,7 +697,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>2042</v>
+        <v>2037</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -710,7 +710,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>2043</v>
+        <v>2038</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -723,7 +723,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>2044</v>
+        <v>2039</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -736,7 +736,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>2045</v>
+        <v>2040</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -749,7 +749,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>2046</v>
+        <v>2041</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -762,7 +762,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>2047</v>
+        <v>2042</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -775,7 +775,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>2048</v>
+        <v>2043</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -788,7 +788,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>2049</v>
+        <v>2044</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -801,7 +801,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -814,7 +814,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>2051</v>
+        <v>2046</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -827,7 +827,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>2052</v>
+        <v>2047</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -840,7 +840,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>2053</v>
+        <v>2048</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -853,7 +853,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>2054</v>
+        <v>2049</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -866,16 +866,81 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
+        <v>2050</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>2051</v>
+      </c>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>2052</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>2053</v>
+      </c>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>2054</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
         <v>2055</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
         <v>2056</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
         <v>2057</v>
       </c>
     </row>
@@ -887,7 +952,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71DE7EE4-731B-47FB-9A4E-667972814602}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="2" customWidth="1"/>
@@ -925,7 +990,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -938,7 +1003,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>2026</v>
+        <v>2021</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -951,7 +1016,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>2027</v>
+        <v>2022</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -964,7 +1029,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>2028</v>
+        <v>2023</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -977,7 +1042,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>2029</v>
+        <v>2024</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -990,7 +1055,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>2030</v>
+        <v>2025</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -1003,7 +1068,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>2031</v>
+        <v>2026</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1016,7 +1081,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>2032</v>
+        <v>2027</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -1029,7 +1094,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>2033</v>
+        <v>2028</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -1042,7 +1107,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>2034</v>
+        <v>2029</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1055,7 +1120,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>2035</v>
+        <v>2030</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1068,7 +1133,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>2036</v>
+        <v>2031</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1081,7 +1146,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>2037</v>
+        <v>2032</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1094,7 +1159,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>2038</v>
+        <v>2033</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1107,7 +1172,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>2039</v>
+        <v>2034</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1120,7 +1185,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>2040</v>
+        <v>2035</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1133,7 +1198,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>2041</v>
+        <v>2036</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1146,7 +1211,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>2042</v>
+        <v>2037</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1159,7 +1224,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>2043</v>
+        <v>2038</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1172,7 +1237,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>2044</v>
+        <v>2039</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1185,7 +1250,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>2045</v>
+        <v>2040</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1198,7 +1263,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>2046</v>
+        <v>2041</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1211,7 +1276,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>2047</v>
+        <v>2042</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1224,7 +1289,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>2048</v>
+        <v>2043</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1237,7 +1302,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>2049</v>
+        <v>2044</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1250,7 +1315,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1263,7 +1328,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>2051</v>
+        <v>2046</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1276,7 +1341,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>2052</v>
+        <v>2047</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1289,7 +1354,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>2053</v>
+        <v>2048</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1302,7 +1367,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>2054</v>
+        <v>2049</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1315,7 +1380,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>2055</v>
+        <v>2050</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1328,7 +1393,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
-        <v>2056</v>
+        <v>2051</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1341,6 +1406,71 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
+        <v>2052</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>2053</v>
+      </c>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>2054</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>2055</v>
+      </c>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>2056</v>
+      </c>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
         <v>2057</v>
       </c>
     </row>
